--- a/tables/Datas/__tables__.xlsx
+++ b/tables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t>activity.xlsx</t>
+  </si>
+  <si>
+    <t>monster.ConfigMonster</t>
+  </si>
+  <si>
+    <t>TbMonster</t>
+  </si>
+  <si>
+    <t>monster.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1097,8 +1106,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1270,6 +1279,20 @@
         <v>42</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/tables/Datas/__tables__.xlsx
+++ b/tables/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -165,6 +165,24 @@
   </si>
   <si>
     <t>monster.xlsx</t>
+  </si>
+  <si>
+    <t>drop.ConfigDrop</t>
+  </si>
+  <si>
+    <t>TbDrop</t>
+  </si>
+  <si>
+    <t>drop.xlsx</t>
+  </si>
+  <si>
+    <t>drop.ConfigDropGroup</t>
+  </si>
+  <si>
+    <t>TbDropGroup</t>
+  </si>
+  <si>
+    <t>dropGroup.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1106,14 +1124,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
     <col min="4" max="4" width="32.425" customWidth="1"/>
     <col min="5" max="5" width="24.3833333333333" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col min="6" max="6" width="27.625" customWidth="1"/>
+    <col min="7" max="7" width="32.125" customWidth="1"/>
+    <col min="8" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="4.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
@@ -1291,6 +1312,34 @@
       </c>
       <c r="E9" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:11">
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Datas/__tables__.xlsx
+++ b/tables/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -183,6 +183,15 @@
   </si>
   <si>
     <t>dropGroup.xlsx</t>
+  </si>
+  <si>
+    <t>monsterRefresh.ConfigMonsterRefresh</t>
+  </si>
+  <si>
+    <t>TbMonsterRefresh</t>
+  </si>
+  <si>
+    <t>monsterRefresh.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
@@ -1342,6 +1351,20 @@
         <v>51</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
